--- a/lin.xlsx
+++ b/lin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\APP\pycharm\program\yolov\yolov1020\lin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B5FA43-887D-4DE7-BC28-19A703AB925D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CF174C-8DC2-4883-BDC2-C6D23D46A556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3519" yWindow="3494" windowWidth="18031" windowHeight="9303" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,10 +116,6 @@
   </si>
   <si>
     <t>说明：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -203,7 +199,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.png</t>
+    <t>eat_ghost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -610,13 +606,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>33</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2</v>
@@ -624,18 +623,6 @@
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
@@ -686,31 +673,31 @@
         <v>17</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.5">
       <c r="E11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.5">
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.5">
       <c r="E13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.5">
@@ -751,7 +738,7 @@
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.5">
       <c r="E19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -762,19 +749,19 @@
     <row r="21" spans="3:6" x14ac:dyDescent="0.5">
       <c r="C21" s="3"/>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.5">
       <c r="C22" s="3"/>
       <c r="E22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.5">
       <c r="C23" s="3"/>
       <c r="E23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
